--- a/output/upload/S00027_2061_e암보험_비갱신형_무배당.xlsx
+++ b/output/upload/S00027_2061_e암보험_비갱신형_무배당.xlsx
@@ -2611,17 +2611,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -2702,17 +2694,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -2793,17 +2777,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -2884,17 +2860,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -2975,17 +2943,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -3066,17 +3026,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -3157,17 +3109,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -3248,17 +3192,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -3338,16 +3274,8 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3391,16 +3319,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3444,16 +3364,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3497,16 +3409,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3550,16 +3454,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3603,16 +3499,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3656,16 +3544,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3709,16 +3589,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3762,16 +3634,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3815,16 +3679,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3868,16 +3724,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3921,16 +3769,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3974,16 +3814,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4027,16 +3859,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4080,16 +3904,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4133,16 +3949,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4186,16 +3994,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4239,16 +4039,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4292,16 +4084,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4345,16 +4129,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4398,16 +4174,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4451,16 +4219,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4504,16 +4264,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4557,16 +4309,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4610,16 +4354,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4663,16 +4399,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4716,16 +4444,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4769,16 +4489,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4822,16 +4534,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4875,16 +4579,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4928,16 +4624,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4981,16 +4669,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5034,16 +4714,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5087,16 +4759,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5140,16 +4804,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5193,16 +4849,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5246,16 +4894,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5299,16 +4939,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5352,16 +4984,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5405,16 +5029,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5458,16 +5074,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5511,16 +5119,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5564,16 +5164,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5617,16 +5209,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5670,16 +5254,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5723,16 +5299,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5776,16 +5344,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5829,16 +5389,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5882,16 +5434,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5935,16 +5479,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5988,16 +5524,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6041,16 +5569,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_2061_e암보험_비갱신형_무배당.xlsx
+++ b/output/upload/S00027_2061_e암보험_비갱신형_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW66"/>
+  <dimension ref="A1:AW76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -3140,15 +3140,15 @@
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3441,11 +3441,11 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3482,15 +3482,15 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3513,12 +3513,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3527,15 +3527,15 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3711,11 +3711,11 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -3783,12 +3783,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3797,15 +3797,15 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -3828,12 +3828,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3842,15 +3842,15 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3981,11 +3981,11 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4008,29 +4008,29 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>N20</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="n">
+        <v>100</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
         <v>20</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N31" t="n">
-        <v>5</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4053,21 +4053,21 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4098,29 +4098,29 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4143,29 +4143,29 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -4278,21 +4278,21 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -4323,21 +4323,21 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -4413,29 +4413,29 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>X60</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L40" t="n">
+        <v>20</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
         <v>60</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>20</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -4458,21 +4458,21 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4521,11 +4521,11 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4548,12 +4548,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4607,7 +4607,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4638,12 +4638,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4683,12 +4683,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4742,15 +4742,15 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4773,12 +4773,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -5043,12 +5043,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5088,12 +5088,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5102,15 +5102,15 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5133,12 +5133,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5178,12 +5178,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5223,12 +5223,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5327,15 +5327,15 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5358,29 +5358,29 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5403,29 +5403,29 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5448,21 +5448,21 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5493,21 +5493,21 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5538,21 +5538,21 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5583,21 +5583,21 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>N20</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -5608,6 +5608,456 @@
         <v>20</v>
       </c>
       <c r="O66" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>100</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>30</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>100</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>60</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>X100</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>100</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>100</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>20</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>5</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>20</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>10</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>20</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>15</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>20</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>20</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>20</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>30</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X60</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>20</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>60</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>20</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>20</v>
+      </c>
+      <c r="O76" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_2061_e암보험_비갱신형_무배당.xlsx
+++ b/output/upload/S00027_2061_e암보험_비갱신형_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2777,11 +2817,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2860,11 +2920,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2943,11 +3023,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3026,11 +3126,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3109,11 +3229,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3192,11 +3332,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3274,8 +3434,31 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3319,8 +3502,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3364,8 +3570,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3409,8 +3638,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3454,8 +3706,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3499,8 +3774,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3544,8 +3842,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3589,8 +3910,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3634,8 +3978,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3679,8 +4046,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3724,8 +4114,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3769,8 +4182,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3814,8 +4250,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3859,8 +4318,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3904,8 +4386,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3949,8 +4454,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3994,8 +4522,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4039,8 +4590,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4084,8 +4658,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4129,8 +4726,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4174,8 +4794,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4219,8 +4862,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4264,8 +4930,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4309,8 +4998,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4354,8 +5066,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4399,8 +5134,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4444,8 +5202,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4489,8 +5270,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4534,8 +5338,31 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4579,8 +5406,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4624,8 +5474,31 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4669,8 +5542,31 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4714,8 +5610,31 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4759,8 +5678,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4804,8 +5746,31 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4849,8 +5814,31 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4894,8 +5882,31 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4939,8 +5950,31 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4984,8 +6018,31 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5029,8 +6086,31 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5074,8 +6154,31 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5119,8 +6222,31 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5164,8 +6290,31 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5209,8 +6358,31 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5254,8 +6426,31 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5299,8 +6494,31 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5344,8 +6562,31 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5389,8 +6630,31 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5434,8 +6698,31 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5479,8 +6766,31 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5524,8 +6834,31 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5569,8 +6902,31 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5614,8 +6970,31 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5659,8 +7038,31 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5704,8 +7106,31 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5749,8 +7174,31 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5794,8 +7242,31 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5839,8 +7310,31 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5884,8 +7378,31 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5929,8 +7446,31 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5974,8 +7514,31 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6019,8 +7582,31 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2061001</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>20611</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_2061_e암보험_비갱신형_무배당.xlsx
+++ b/output/upload/S00027_2061_e암보험_비갱신형_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>2061001</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">

--- a/output/upload/S00027_2061_e암보험_비갱신형_무배당.xlsx
+++ b/output/upload/S00027_2061_e암보험_비갱신형_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW76"/>
+  <dimension ref="A1:AW72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3266,12 +3266,12 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -3280,15 +3280,15 @@
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3629,7 +3629,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3693,11 +3693,11 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3811,12 +3811,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3825,15 +3825,15 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -4169,11 +4169,11 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -4287,12 +4287,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4301,15 +4301,15 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4645,11 +4645,11 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4763,29 +4763,29 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5121,11 +5121,11 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -5136,22 +5136,22 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5171,29 +5171,29 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>60</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L40" t="n">
-        <v>20</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="N40" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -5204,22 +5204,22 @@
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5239,29 +5239,29 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>60</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L41" t="n">
-        <v>20</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="N41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -5272,22 +5272,22 @@
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -5340,22 +5340,22 @@
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -5408,22 +5408,22 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5476,22 +5476,22 @@
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5529,11 +5529,11 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -5544,22 +5544,22 @@
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -5612,22 +5612,22 @@
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5661,15 +5661,15 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -5680,22 +5680,22 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5729,15 +5729,15 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -5748,22 +5748,22 @@
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -5816,22 +5816,22 @@
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -5884,22 +5884,22 @@
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5937,11 +5937,11 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -5952,22 +5952,22 @@
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6005,11 +6005,11 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -6020,22 +6020,22 @@
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -6088,22 +6088,22 @@
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -6137,15 +6137,15 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -6156,22 +6156,22 @@
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -6205,15 +6205,15 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -6224,22 +6224,22 @@
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -6292,22 +6292,22 @@
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -6360,22 +6360,22 @@
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -6413,11 +6413,11 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -6428,22 +6428,22 @@
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6481,11 +6481,11 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -6496,22 +6496,22 @@
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6531,12 +6531,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -6564,22 +6564,22 @@
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6613,15 +6613,15 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -6632,22 +6632,22 @@
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6667,12 +6667,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6681,15 +6681,15 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -6700,22 +6700,22 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -6768,22 +6768,22 @@
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -6836,22 +6836,22 @@
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6889,11 +6889,11 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -6904,22 +6904,22 @@
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6957,11 +6957,11 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -6972,22 +6972,22 @@
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7007,21 +7007,21 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -7040,22 +7040,22 @@
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7075,29 +7075,29 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -7108,22 +7108,22 @@
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7143,29 +7143,29 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -7176,22 +7176,22 @@
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -7244,22 +7244,22 @@
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -7312,22 +7312,22 @@
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7365,285 +7365,13 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O72" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>20</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N73" t="n">
-        <v>20</v>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>N30</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L74" t="n">
-        <v>20</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N74" t="n">
-        <v>30</v>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>X60</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L75" t="n">
-        <v>20</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N75" t="n">
-        <v>60</v>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2061001</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
-        <v>20</v>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N76" t="n">
-        <v>20</v>
-      </c>
-      <c r="O76" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_2061_e암보험_비갱신형_무배당.xlsx
+++ b/output/upload/S00027_2061_e암보험_비갱신형_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW72"/>
+  <dimension ref="A1:AW64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="L8" s="6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -2854,29 +2854,29 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
+          <t>X70</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
           <t>X60</t>
         </is>
       </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="n">
         <v>60</v>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>15</v>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
@@ -2957,12 +2957,12 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="L10" s="6" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="N10" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -3074,7 +3074,7 @@
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="N11" s="6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
@@ -3163,12 +3163,12 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -3177,15 +3177,15 @@
         </is>
       </c>
       <c r="L12" s="6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -3276,11 +3276,11 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3489,11 +3489,11 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -3607,12 +3607,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3621,15 +3621,15 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3689,15 +3689,15 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -3743,12 +3743,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3757,15 +3757,15 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3879,12 +3879,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3965,11 +3965,11 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -4083,21 +4083,21 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -4165,15 +4165,15 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -4219,12 +4219,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -4233,15 +4233,15 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4373,11 +4373,11 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4509,11 +4509,11 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -4559,12 +4559,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4713,11 +4713,11 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -4763,29 +4763,29 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>100</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L34" t="n">
-        <v>20</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -4864,22 +4864,22 @@
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4899,29 +4899,29 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>70</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L36" t="n">
-        <v>20</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="N36" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -4932,22 +4932,22 @@
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4967,29 +4967,29 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>70</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L37" t="n">
-        <v>20</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="N37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -5000,22 +5000,22 @@
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5035,29 +5035,29 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -5068,22 +5068,22 @@
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2061001</t>
+          <t>2061002</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[표준체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
+          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5103,29 +5103,29 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>100</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L39" t="n">
-        <v>20</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="N39" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -5171,12 +5171,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -5239,12 +5239,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -5307,21 +5307,21 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -5443,12 +5443,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -5457,15 +5457,15 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -5529,11 +5529,11 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5593,15 +5593,15 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -5647,12 +5647,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5729,7 +5729,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -5783,12 +5783,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -5987,12 +5987,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>X70</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6001,15 +6001,15 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -6055,21 +6055,21 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -6123,12 +6123,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -6259,12 +6259,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -6327,12 +6327,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -6341,15 +6341,15 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -6395,12 +6395,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>X60</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -6409,15 +6409,15 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X100</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>X80</t>
+          <t>X60</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -6531,12 +6531,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X70</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -6599,12 +6599,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>X80</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6613,15 +6613,15 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6689,7 +6689,7 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N30</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -6803,21 +6803,21 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X100</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>N30</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -6825,553 +6825,9 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="O64" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>X60</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>100</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N65" t="n">
-        <v>60</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>X100</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>100</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>100</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>20</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N67" t="n">
-        <v>5</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>20</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N68" t="n">
-        <v>10</v>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>20</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N69" t="n">
-        <v>15</v>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>20</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N70" t="n">
-        <v>20</v>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>N30</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
-        <v>20</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N71" t="n">
-        <v>30</v>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2061002</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>한화생명 e암보험(비갱신형) 무배당[비흡연체형](해약환급금 미지급형(납입기간중 0%, 납입기간후 50%))</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>X60</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
-        <v>20</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="N72" t="n">
-        <v>60</v>
-      </c>
-      <c r="O72" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
